--- a/scripts/checks/results/HLR_results_06_Dunn_lgs_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_06_Dunn_lgs_noLgArea_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3059604222665624</v>
+        <v>0.2773093265883012</v>
       </c>
       <c r="H2" t="n">
-        <v>45.84736222052121</v>
+        <v>45.27870877721755</v>
       </c>
       <c r="I2" t="n">
-        <v>7.810452239193904e-10</v>
+        <v>6.498545364230793e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>14.92839846445508</v>
+        <v>17.9167062783317</v>
       </c>
       <c r="K2" t="n">
-        <v>21.50943396226416</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>6.581035497809081</v>
+        <v>6.874960388334969</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1435422929274527</v>
+        <v>0.151836493884167</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2048517520215634</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.8769068789051704, 'N1ratio-ArgsPreds': -0.25892073248774317}</t>
+          <t>{'const': 0.7704480129557647, 'N1ratio-ArgsPreds': -3.197547552292713}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.7265771913199485e-15, 'N1ratio-ArgsPreds': 7.810452239194086e-10}</t>
+          <t>{'const': 1.1179374076442262e-16, 'N1ratio-ArgsPreds': 6.498545364231103e-10}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5531368928814658}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5266016773504437}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5531368928814663)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504444)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5531368928814662)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504445)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.596042226656255)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(27.730932658830167)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E3" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3476503175884775</v>
+        <v>0.3409001611077889</v>
       </c>
       <c r="H3" t="n">
-        <v>27.44538985536318</v>
+        <v>30.25741814521527</v>
       </c>
       <c r="I3" t="n">
-        <v>2.790894677522507e-10</v>
+        <v>2.56239171087869e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>14.03167241413464</v>
+        <v>16.3401835058694</v>
       </c>
       <c r="K3" t="n">
-        <v>21.50943396226416</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>3.738880774064759</v>
+        <v>4.225741580398633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1362298292634431</v>
+        <v>0.1396596880843539</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2048517520215634</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.9611211826011918, 'N1ratio-ArgsPreds': -0.24402541624977742, 'Fam_class': -0.002986968938184703}</t>
+          <t>{'const': 0.8799286099669941, 'N1ratio-ArgsPreds': -2.9673419173463604, 'Fam_class': -0.0032709757323482725}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 2.3183274008404673e-16, 'N1ratio-ArgsPreds': 3.3230185967641215e-09, 'Fam_class': 0.011738588428515356}</t>
+          <t>{'const': 7.958996084822624e-19, 'N1ratio-ArgsPreds': 2.769771222493802e-09, 'Fam_class': 0.0010536502492942584}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5213157680793211, 'Fam_class': -0.20664578221098165}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48868928620825386, 'Fam_class': -0.25500624290711527}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5377063438432251), 'Fam_class': np.float64(-0.24508869754796073)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5114951182194193), 'Fam_class': np.float64(-0.29663407450257134)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5150978272666621), 'Fam_class': np.float64(-0.20418103565687704)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48325823941642665), 'Fam_class': np.float64(-0.25217223185649845)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(26.532577165483605), 'Fam_class': np.float64(4.168989532191489)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.353852596386435), 'Fam_class': np.float64(6.359083451948762)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.04168989532191514</v>
+        <v>0.06359083451948766</v>
       </c>
       <c r="V3" t="n">
-        <v>6.582450078435745</v>
+        <v>11.28831657929871</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01173858842851501</v>
+        <v>0.001053650249293891</v>
       </c>
     </row>
     <row r="4">
@@ -717,76 +717,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.385300383471343</v>
+        <v>0.3737952637902542</v>
       </c>
       <c r="H4" t="n">
-        <v>15.82697373001836</v>
+        <v>17.16150200175148</v>
       </c>
       <c r="I4" t="n">
-        <v>4.348452555930206e-10</v>
+        <v>4.605128891517196e-11</v>
       </c>
       <c r="J4" t="n">
-        <v>13.22184080835225</v>
+        <v>15.52465908519995</v>
       </c>
       <c r="K4" t="n">
-        <v>21.50943396226416</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="L4" t="n">
-        <v>2.071898288477977</v>
+        <v>2.31675189536668</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1309093149341807</v>
+        <v>0.1349970355234778</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2048517520215634</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.32115969184216225, 'N1ratio-ArgsPreds': -0.24097144022603018, 'Fam_class': -0.004198280584489031, 'Nlen_freq': 0.0665226125352025, 'Vlen_freq': 0.03859494108704595}</t>
+          <t>{'const': 0.5521715457673296, 'N1ratio-ArgsPreds': -3.128561069294144, 'Fam_class': -0.004428884851281784, 'Nlen_freq': 1.084398461997396, 'Vlen_freq': -0.11531662867195097}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 0.2500604067687615, 'N1ratio-ArgsPreds': 4.555851648895976e-09, 'Fam_class': 0.0015041401648152699, 'Nlen_freq': 0.284541420527386, 'Vlen_freq': 0.4288129414549008}</t>
+          <t>{'const': 0.0009824642341280197, 'N1ratio-ArgsPreds': 7.79028650706584e-10, 'Fam_class': 6.579090313453102e-05, 'Nlen_freq': 0.052268660638574424, 'Vlen_freq': 0.8301853260309251}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5147915056439443, 'Fam_class': -0.290447270553192, 'Nlen_freq': 0.13501304546534035, 'Vlen_freq': 0.09186389135352444}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5152403458714151, 'Fam_class': -0.34527718289820536, 'Nlen_freq': 0.22129263053817488, 'Vlen_freq': -0.02267583506274776}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5381548069864609), 'Fam_class': np.float64(-0.3088196545880341), 'Nlen_freq': np.float64(0.10644645164129195), 'Vlen_freq': np.float64(0.07880205305998178)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5302968506272241), 'Fam_class': np.float64(-0.36036268215345424), 'Nlen_freq': np.float64(0.17990228282417076), 'Vlen_freq': np.float64(-0.02004036903938752)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5005995531278766), 'Fam_class': np.float64(-0.2545662411320843), 'Nlen_freq': np.float64(0.08393385455360595), 'Vlen_freq': np.float64(0.0619757285440557)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.49496859398886983), 'Fam_class': np.float64(-0.30570583844472), 'Nlen_freq': np.float64(0.14472348969996685), 'Vlen_freq': np.float64(-0.015861750567287412)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(25.05999125918298), 'Fam_class': np.float64(6.48039711241185), 'Nlen_freq': np.float64(0.7044891940225879), 'Vlen_freq': np.float64(0.384099092856648)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(24.499390903531868), 'Fam_class': np.float64(9.345605965918924), 'Nlen_freq': np.float64(2.094488847093641), 'Vlen_freq': np.float64(0.025159513105884258)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03765006588286546</v>
+        <v>0.03289510268246532</v>
       </c>
       <c r="V4" t="n">
-        <v>3.093101534407849</v>
+        <v>3.020527145307653</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04968388965636977</v>
+        <v>0.05266179955841151</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_06_Dunn_lgs_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_06_Dunn_lgs_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2773093265883012</v>
+        <v>0.2778077214292567</v>
       </c>
       <c r="H2" t="n">
-        <v>45.27870877721755</v>
+        <v>45.39138966360625</v>
       </c>
       <c r="I2" t="n">
-        <v>6.498545364230793e-10</v>
+        <v>6.23405371411057e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>17.9167062783317</v>
+        <v>17.90435023956635</v>
       </c>
       <c r="K2" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>6.874960388334969</v>
+        <v>6.887316427100323</v>
       </c>
       <c r="M2" t="n">
-        <v>0.151836493884167</v>
+        <v>0.1517317816912402</v>
       </c>
       <c r="N2" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7704480129557647, 'N1ratio-ArgsPreds': -3.197547552292713}</t>
+          <t>{'const': 0.7491199802103012, 'N1ratio-ArgsPreds': -3.0224806007943616}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 1.1179374076442262e-16, 'N1ratio-ArgsPreds': 6.498545364231103e-10}</t>
+          <t>{'const': 6.899475278910947e-17, 'N1ratio-ArgsPreds': 6.234053714110714e-10}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5266016773504437}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5270746829712618}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504444)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266016773504445)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.730932658830167)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(27.78077214292572)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3409001611077889</v>
+        <v>0.3468783875246924</v>
       </c>
       <c r="H3" t="n">
-        <v>30.25741814521527</v>
+        <v>31.06984255701949</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56239171087869e-11</v>
+        <v>1.503668952114882e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>16.3401835058694</v>
+        <v>16.19197330928367</v>
       </c>
       <c r="K3" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>4.225741580398633</v>
+        <v>4.2998466786915</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1396596880843539</v>
+        <v>0.1383929342673818</v>
       </c>
       <c r="N3" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.8799286099669941, 'N1ratio-ArgsPreds': -2.9673419173463604, 'Fam_class': -0.0032709757323482725}</t>
+          <t>{'const': 0.8694669476332118, 'N1ratio-ArgsPreds': -2.8294009162073523, 'Fam_class': -0.0033986661667828}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 7.958996084822624e-19, 'N1ratio-ArgsPreds': 2.769771222493802e-09, 'Fam_class': 0.0010536502492942584}</t>
+          <t>{'const': 3.437321412929333e-19, 'N1ratio-ArgsPreds': 1.606111944602189e-09, 'Fam_class': 0.0006209671097238488}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48868928620825386, 'Fam_class': -0.25500624290711527}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49340452028596854, 'Fam_class': -0.2649610272298194}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5114951182194193), 'Fam_class': np.float64(-0.29663407450257134)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5180004928438996), 'Fam_class': np.float64(-0.30925761460178797)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48325823941642665), 'Fam_class': np.float64(-0.25217223185649845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48940448749553883), 'Fam_class': np.float64(-0.2628129869230889)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.353852596386435), 'Fam_class': np.float64(6.359083451948762)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.9516752380771), 'Fam_class': np.float64(6.907066609543571)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.06359083451948766</v>
+        <v>0.06907066609543566</v>
       </c>
       <c r="V3" t="n">
-        <v>11.28831657929871</v>
+        <v>12.37329737495327</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001053650249293891</v>
+        <v>0.0006209671097233587</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3737952637902542</v>
+        <v>0.3691894513850984</v>
       </c>
       <c r="H4" t="n">
-        <v>17.16150200175148</v>
+        <v>16.82628286833128</v>
       </c>
       <c r="I4" t="n">
-        <v>4.605128891517196e-11</v>
+        <v>6.935815553853807e-11</v>
       </c>
       <c r="J4" t="n">
-        <v>15.52465908519995</v>
+        <v>15.63884485107777</v>
       </c>
       <c r="K4" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L4" t="n">
-        <v>2.31675189536668</v>
+        <v>2.288205453897225</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1349970355234778</v>
+        <v>0.1359899552267632</v>
       </c>
       <c r="N4" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5521715457673296, 'N1ratio-ArgsPreds': -3.128561069294144, 'Fam_class': -0.004428884851281784, 'Nlen_freq': 1.084398461997396, 'Vlen_freq': -0.11531662867195097}</t>
+          <t>{'const': 0.5977560056272649, 'N1ratio-ArgsPreds': -2.924861938504255, 'Fam_class': -0.0043922197080065815, 'Nlen_freq': 0.8203208602381116, 'Vlen_freq': -0.006560937979058101}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 0.0009824642341280197, 'N1ratio-ArgsPreds': 7.79028650706584e-10, 'Fam_class': 6.579090313453102e-05, 'Nlen_freq': 0.052268660638574424, 'Vlen_freq': 0.8301853260309251}</t>
+          <t>{'const': 0.00031141796459685956, 'N1ratio-ArgsPreds': 1.0693956086186703e-09, 'Fam_class': 8.440366515143027e-05, 'Nlen_freq': 0.1360520376486196, 'Vlen_freq': 0.9901938475958582}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5152403458714151, 'Fam_class': -0.34527718289820536, 'Nlen_freq': 0.22129263053817488, 'Vlen_freq': -0.02267583506274776}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5100514718164527, 'Fam_class': -0.3424187574015576, 'Nlen_freq': 0.1709668077643407, 'Vlen_freq': -0.0013124191132613985}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5302968506272241), 'Fam_class': np.float64(-0.36036268215345424), 'Nlen_freq': np.float64(0.17990228282417076), 'Vlen_freq': np.float64(-0.02004036903938752)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266177583113482), 'Fam_class': np.float64(-0.355349646334466), 'Nlen_freq': np.float64(0.13863320362667286), 'Vlen_freq': np.float64(-0.0011485887384872213)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49496859398886983), 'Fam_class': np.float64(-0.30570583844472), 'Nlen_freq': np.float64(0.14472348969996685), 'Vlen_freq': np.float64(-0.015861750567287412)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4920098956226388), 'Fam_class': np.float64(-0.30193786169875597), 'Nlen_freq': np.float64(0.11118104391672569), 'Vlen_freq': np.float64(-0.0009122509281421551)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.499390903531868), 'Fam_class': np.float64(9.345605965918924), 'Nlen_freq': np.float64(2.094488847093641), 'Vlen_freq': np.float64(0.025159513105884258)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(24.207373739059992), 'Fam_class': np.float64(9.116647232721709), 'Nlen_freq': np.float64(1.2361224526412886), 'Vlen_freq': np.float64(8.322017558962236e-05)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03289510268246532</v>
+        <v>0.02231106386040604</v>
       </c>
       <c r="V4" t="n">
-        <v>3.020527145307653</v>
+        <v>2.033710715190539</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05266179955841151</v>
+        <v>0.1355287031498066</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_06_Dunn_lgs_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_06_Dunn_lgs_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2778077214292567</v>
+        <v>0.2755848639634494</v>
       </c>
       <c r="H2" t="n">
-        <v>45.39138966360625</v>
+        <v>44.89002552542782</v>
       </c>
       <c r="I2" t="n">
-        <v>6.23405371411057e-10</v>
+        <v>7.501800790435129e-10</v>
       </c>
       <c r="J2" t="n">
-        <v>17.90435023956635</v>
+        <v>17.95945858090615</v>
       </c>
       <c r="K2" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>6.887316427100323</v>
+        <v>6.832208085760517</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1517317816912402</v>
+        <v>0.152198801533103</v>
       </c>
       <c r="N2" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7491199802103012, 'N1ratio-ArgsPreds': -3.0224806007943616}</t>
+          <t>{'const': 0.7461726021992878, 'N1ratio-ArgsPreds': -3.0029926664449578}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 6.899475278910947e-17, 'N1ratio-ArgsPreds': 6.234053714110714e-10}</t>
+          <t>{'const': 8.338478385942126e-17, 'N1ratio-ArgsPreds': 7.501800790435231e-10}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5270746829712618}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5249617738116265}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5249617738116272)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5270746829712628)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5249617738116275)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(27.78077214292572)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(27.558486396345028)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3468783875246924</v>
+        <v>0.3445557602744161</v>
       </c>
       <c r="H3" t="n">
-        <v>31.06984255701949</v>
+        <v>30.75244354041819</v>
       </c>
       <c r="I3" t="n">
-        <v>1.503668952114882e-11</v>
+        <v>1.850723068995827e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>16.19197330928367</v>
+        <v>16.24955510986344</v>
       </c>
       <c r="K3" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2998466786915</v>
+        <v>4.271055778401617</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1383929342673818</v>
+        <v>0.1388850864090892</v>
       </c>
       <c r="N3" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.8694669476332118, 'N1ratio-ArgsPreds': -2.8294009162073523, 'Fam_class': -0.0033986661667828}</t>
+          <t>{'const': 0.8663052721193276, 'N1ratio-ArgsPreds': -2.8090928899172782, 'Fam_class': -0.003396620212338761}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.437321412929333e-19, 'N1ratio-ArgsPreds': 1.606111944602189e-09, 'Fam_class': 0.0006209671097238488}</t>
+          <t>{'const': 4.2574190185320626e-19, 'N1ratio-ArgsPreds': 1.985915714426193e-09, 'Fam_class': 0.0006397822330810478}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49340452028596854, 'Fam_class': -0.2649610272298194}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49106559691947604, 'Fam_class': -0.2648015240116286}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5180004928438996), 'Fam_class': np.float64(-0.30925761460178797)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.51548281300043), 'Fam_class': np.float64(-0.3085596810744864)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48940448749553883), 'Fam_class': np.float64(-0.2628129869230889)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.487025795138713), 'Fam_class': np.float64(-0.26262310696312885)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.9516752380771), 'Fam_class': np.float64(6.907066609543571)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.71941251304957), 'Fam_class': np.float64(6.897089631096702)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.06907066609543566</v>
+        <v>0.06897089631096676</v>
       </c>
       <c r="V3" t="n">
-        <v>12.37329737495327</v>
+        <v>12.3116420578532</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006209671097233587</v>
+        <v>0.0006397822330816575</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3691894513850984</v>
+        <v>0.3663202017292058</v>
       </c>
       <c r="H4" t="n">
-        <v>16.82628286833128</v>
+        <v>16.61991723336284</v>
       </c>
       <c r="I4" t="n">
-        <v>6.935815553853807e-11</v>
+        <v>8.936958339879814e-11</v>
       </c>
       <c r="J4" t="n">
-        <v>15.63884485107777</v>
+        <v>15.70997833213011</v>
       </c>
       <c r="K4" t="n">
         <v>24.79166666666667</v>
       </c>
       <c r="L4" t="n">
-        <v>2.288205453897225</v>
+        <v>2.27042208363414</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1359899552267632</v>
+        <v>0.136608507235914</v>
       </c>
       <c r="N4" t="n">
         <v>0.2083333333333334</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5977560056272649, 'N1ratio-ArgsPreds': -2.924861938504255, 'Fam_class': -0.0043922197080065815, 'Nlen_freq': 0.8203208602381116, 'Vlen_freq': -0.006560937979058101}</t>
+          <t>{'const': 0.5990685588108, 'N1ratio-ArgsPreds': -2.906385706222835, 'Fam_class': -0.004380835437338037, 'Nlen_freq': 0.8233815112104019, 'Vlen_freq': -0.010938869917355931}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 0.00031141796459685956, 'N1ratio-ArgsPreds': 1.0693956086186703e-09, 'Fam_class': 8.440366515143027e-05, 'Nlen_freq': 0.1360520376486196, 'Vlen_freq': 0.9901938475958582}</t>
+          <t>{'const': 0.0003009232320317954, 'N1ratio-ArgsPreds': 1.3713486920240034e-09, 'Fam_class': 9.194176802581494e-05, 'Nlen_freq': 0.14114056459305818, 'Vlen_freq': 0.9837106154199469}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5100514718164527, 'Fam_class': -0.3424187574015576, 'Nlen_freq': 0.1709668077643407, 'Vlen_freq': -0.0013124191132613985}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5080736336015497, 'Fam_class': -0.34153123626750775, 'Nlen_freq': 0.16968948058266534, 'Vlen_freq': -0.0021909689942372}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5266177583113482), 'Fam_class': np.float64(-0.355349646334466), 'Nlen_freq': np.float64(0.13863320362667286), 'Vlen_freq': np.float64(-0.0011485887384872213)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5236983787040976), 'Fam_class': np.float64(-0.35360885616207377), 'Nlen_freq': np.float64(0.13687389675655173), 'Vlen_freq': np.float64(-0.0019080492418700784)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4920098956226388), 'Fam_class': np.float64(-0.30193786169875597), 'Nlen_freq': np.float64(0.11118104391672569), 'Vlen_freq': np.float64(-0.0009122509281421551)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4893568002384654), 'Fam_class': np.float64(-0.3009288130003524), 'Nlen_freq': np.float64(0.10999230156854993), 'Vlen_freq': np.float64(-0.0015188864231946882)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.207373739059992), 'Fam_class': np.float64(9.116647232721709), 'Nlen_freq': np.float64(1.2361224526412886), 'Vlen_freq': np.float64(8.322017558962236e-05)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.947007793962932), 'Fam_class': np.float64(9.055815049380106), 'Nlen_freq': np.float64(1.2098306404346832), 'Vlen_freq': np.float64(0.00023070159665651533)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.02231106386040604</v>
+        <v>0.02176444145478962</v>
       </c>
       <c r="V4" t="n">
-        <v>2.033710715190539</v>
+        <v>1.974901814868352</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1355287031498066</v>
+        <v>0.1434535761282482</v>
       </c>
     </row>
   </sheetData>
